--- a/data/trans_orig/IP05A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A04-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112271</t>
+          <t>110933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125125</t>
+          <t>124936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132511</t>
+          <t>132130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143270</t>
+          <t>143521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249340</t>
+          <t>249201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266413</t>
+          <t>265863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164704</t>
+          <t>164753</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178949</t>
+          <t>178532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184521</t>
+          <t>184668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198685</t>
+          <t>199133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354380</t>
+          <t>355031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373795</t>
+          <t>374634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>26858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>43288</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114833</t>
+          <t>114398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126167</t>
+          <t>126082</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123291</t>
+          <t>123871</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136149</t>
+          <t>135865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>241605</t>
+          <t>240123</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>258934</t>
+          <t>258691</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167918</t>
+          <t>167834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184690</t>
+          <t>183759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166932</t>
+          <t>168685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183193</t>
+          <t>183835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341171</t>
+          <t>340555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363928</t>
+          <t>363515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>29755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>31288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34280</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55154</t>
+          <t>55388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>573912</t>
+          <t>574508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>623553</t>
+          <t>623906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>650370</t>
+          <t>650920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1208496</t>
+          <t>1208356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1248268</t>
+          <t>1245957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59322</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116951</t>
+          <t>116636</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>152062</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132852</t>
+          <t>132515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138616</t>
+          <t>138626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142487</t>
+          <t>143210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>150774</t>
+          <t>150914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>278689</t>
+          <t>278084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>287984</t>
+          <t>287978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>741</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183688</t>
+          <t>183966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195620</t>
+          <t>195462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194246</t>
+          <t>194897</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209310</t>
+          <t>209063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>383623</t>
+          <t>382482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401428</t>
+          <t>401876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35006</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138644</t>
+          <t>138806</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148908</t>
+          <t>148427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146710</t>
+          <t>146613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158114</t>
+          <t>158098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>290275</t>
+          <t>289477</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>304011</t>
+          <t>304645</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>177686</t>
+          <t>177405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192685</t>
+          <t>193448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172881</t>
+          <t>173377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188570</t>
+          <t>189196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>356211</t>
+          <t>356973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377798</t>
+          <t>378888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23986</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>26999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>27455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>646380</t>
+          <t>646724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>667901</t>
+          <t>667802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>672015</t>
+          <t>671651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>697058</t>
+          <t>697178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1325130</t>
+          <t>1323890</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1360383</t>
+          <t>1358863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>75769</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>107377</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123494</t>
+          <t>124174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131184</t>
+          <t>131648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>138227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145906</t>
+          <t>145984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266508</t>
+          <t>265824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275975</t>
+          <t>276082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174129</t>
+          <t>172945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188066</t>
+          <t>188659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192661</t>
+          <t>193124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206972</t>
+          <t>207172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>372675</t>
+          <t>371256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392377</t>
+          <t>392211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25059</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119332</t>
+          <t>119014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>133283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>128494</t>
+          <t>128817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145073</t>
+          <t>145661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252155</t>
+          <t>253397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274084</t>
+          <t>275078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44150</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189181</t>
+          <t>189436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199811</t>
+          <t>199850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176779</t>
+          <t>176934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190320</t>
+          <t>189979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370764</t>
+          <t>371556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387815</t>
+          <t>387365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34966</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>619370</t>
+          <t>620090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>644709</t>
+          <t>643246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>652796</t>
+          <t>651138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>679181</t>
+          <t>678489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1279691</t>
+          <t>1280034</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1315677</t>
+          <t>1316402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>64958</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83754</t>
+          <t>82953</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110712</t>
+          <t>110496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116237</t>
+          <t>116282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137125</t>
+          <t>137015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250066</t>
+          <t>249653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>255722</t>
+          <t>255678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174868</t>
+          <t>174083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185238</t>
+          <t>184733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230019</t>
+          <t>230877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245047</t>
+          <t>245655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408994</t>
+          <t>409758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427473</t>
+          <t>427727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>177564</t>
+          <t>176907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186227</t>
+          <t>186172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167197</t>
+          <t>168265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>180068</t>
+          <t>180073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>348910</t>
+          <t>349095</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364426</t>
+          <t>364729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152229</t>
+          <t>151669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161468</t>
+          <t>161554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164045</t>
+          <t>163879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174754</t>
+          <t>174831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320020</t>
+          <t>320095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334256</t>
+          <t>334854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>625845</t>
+          <t>625985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>643144</t>
+          <t>643683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711773</t>
+          <t>711808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>734682</t>
+          <t>734022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1345484</t>
+          <t>1344876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1372326</t>
+          <t>1373396</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,82 +10334,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9633</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16972</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>9633</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5229</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17143</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>11695</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>27136</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>18039</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>11517</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
